--- a/Mediciones/Motor_Param.xlsx
+++ b/Mediciones/Motor_Param.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8fa820dbf13b2b2e/Escritorio/8vo Semestre/Sistemas de Control Automático 2/Git_PID/PID_Control_SCA2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8fa820dbf13b2b2e/Escritorio/8vo Semestre/Sistemas de Control Automático 2/Git_PID/PID_Control_SCA2/Mediciones/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="274" documentId="8_{7C12B4B4-DE19-40FC-974C-A4044854BDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67BB4201-574A-4054-9BF7-B98A4B76A1F4}"/>
+  <xr:revisionPtr revIDLastSave="275" documentId="8_{7C12B4B4-DE19-40FC-974C-A4044854BDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77D72203-69F6-4FCC-88D4-43D23984E168}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{3505C609-621A-4D72-85AF-8C3EF7124E8D}"/>
   </bookViews>
@@ -208,7 +208,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -218,6 +218,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -234,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -255,6 +261,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3653,19 +3660,19 @@
       </c>
     </row>
     <row r="8" spans="2:12">
-      <c r="B8" s="1">
+      <c r="B8" s="8">
         <v>20</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="8">
         <v>1</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="8">
         <v>0.4</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="8" t="s">
         <v>25</v>
       </c>
       <c r="H8">
